--- a/游戏设计王/宾果数学-Bingo机率与RTP模型.xlsx
+++ b/游戏设计王/宾果数学-Bingo机率与RTP模型.xlsx
@@ -874,11 +874,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="31">
     <font>
@@ -1584,7 +1585,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1714,6 +1715,18 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -7132,7 +7145,7 @@
         <f t="shared" ref="B14:B28" si="0">IF(OR($B$4-A14&lt;0,$B$4&gt;$B$3),0,COMBIN($B$3-A14,$B$4-A14))</f>
         <v>2.2437765816886e+23</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="44">
         <f t="shared" ref="C14:C28" si="1">IF(OR($B$4-A14&lt;0,$B$10=0),0,B14/$B$10)</f>
         <v>0.333333333333333</v>
       </c>
@@ -7158,7 +7171,7 @@
         <f t="shared" si="0"/>
         <v>7.31118212010893e+22</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="44">
         <f t="shared" si="1"/>
         <v>0.108614232209738</v>
       </c>
@@ -7184,7 +7197,7 @@
         <f t="shared" si="0"/>
         <v>2.32628522003466e+22</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="44">
         <f t="shared" si="1"/>
         <v>0.0345590738849166</v>
       </c>
@@ -7210,7 +7223,7 @@
         <f t="shared" si="0"/>
         <v>7.21950585527997e+21</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="44">
         <f t="shared" si="1"/>
         <v>0.0107252298263534</v>
       </c>
@@ -7236,7 +7249,7 @@
         <f t="shared" si="0"/>
         <v>2.18264130508464e+21</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="44">
         <f t="shared" si="1"/>
         <v>0.00324251134285104</v>
       </c>
@@ -7262,7 +7275,7 @@
         <f t="shared" si="0"/>
         <v>6.41953325024895e+20</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="44">
         <f t="shared" si="1"/>
         <v>0.000953679806720893</v>
       </c>
@@ -7288,7 +7301,7 @@
         <f t="shared" si="0"/>
         <v>1.83415235721399e+20</v>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="44">
         <f t="shared" si="1"/>
         <v>0.000272479944777398</v>
       </c>
@@ -7314,7 +7327,7 @@
         <f t="shared" si="0"/>
         <v>5.08259086938815e+19</v>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="44">
         <f t="shared" si="1"/>
         <v>7.55064907214476e-5</v>
       </c>
@@ -7340,7 +7353,7 @@
         <f t="shared" si="0"/>
         <v>1.36362194056755e+19</v>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="44">
         <f t="shared" si="1"/>
         <v>2.02578389740469e-5</v>
       </c>
@@ -7366,7 +7379,7 @@
         <f t="shared" si="0"/>
         <v>3.53531614221217e+18</v>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="44">
         <f t="shared" si="1"/>
         <v>5.25203232660476e-6</v>
       </c>
@@ -7392,7 +7405,7 @@
         <f t="shared" si="0"/>
         <v>8.83829035553044e+17</v>
       </c>
-      <c r="C24" s="11">
+      <c r="C24" s="44">
         <f t="shared" si="1"/>
         <v>1.31300808165119e-6</v>
       </c>
@@ -7418,7 +7431,7 @@
         <f t="shared" si="0"/>
         <v>2.12566476905162e+17</v>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="44">
         <f t="shared" si="1"/>
         <v>3.15786753814843e-7</v>
       </c>
@@ -7444,7 +7457,7 @@
         <f t="shared" si="0"/>
         <v>4.90538023627298e+16</v>
       </c>
-      <c r="C26" s="11">
+      <c r="C26" s="44">
         <f t="shared" si="1"/>
         <v>7.28738662649638e-8</v>
       </c>
@@ -7470,7 +7483,7 @@
         <f t="shared" si="0"/>
         <v>1.08300602619014e+16</v>
       </c>
-      <c r="C27" s="11">
+      <c r="C27" s="44">
         <f t="shared" si="1"/>
         <v>1.60890354091478e-8</v>
       </c>
@@ -7496,7 +7509,7 @@
         <f t="shared" si="0"/>
         <v>2280012686716080</v>
       </c>
-      <c r="C28" s="11">
+      <c r="C28" s="44">
         <f t="shared" si="1"/>
         <v>3.38716534929428e-9</v>
       </c>
@@ -7587,7 +7600,7 @@
       <c r="C32" s="10">
         <v>4</v>
       </c>
-      <c r="D32" s="11">
+      <c r="D32" s="44">
         <f>C17</f>
         <v>0.0107252298263534</v>
       </c>
@@ -7611,7 +7624,7 @@
       <c r="C33" s="10">
         <v>5</v>
       </c>
-      <c r="D33" s="11">
+      <c r="D33" s="44">
         <f>C18</f>
         <v>0.00324251134285104</v>
       </c>
@@ -7635,7 +7648,7 @@
       <c r="C34" s="10">
         <v>3</v>
       </c>
-      <c r="D34" s="11">
+      <c r="D34" s="44">
         <f>C16</f>
         <v>0.0345590738849166</v>
       </c>
@@ -7659,7 +7672,7 @@
       <c r="C35" s="10">
         <v>12</v>
       </c>
-      <c r="D35" s="11">
+      <c r="D35" s="44">
         <f>C25</f>
         <v>3.15786753814843e-7</v>
       </c>
@@ -7683,7 +7696,7 @@
       <c r="C36" s="10">
         <v>15</v>
       </c>
-      <c r="D36" s="11">
+      <c r="D36" s="44">
         <f>C28</f>
         <v>3.38716534929428e-9</v>
       </c>
@@ -7767,7 +7780,7 @@
       <c r="B40" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="C40" s="11">
+      <c r="C40" s="44">
         <f>3*C18-3*C23+C28</f>
         <v>0.00971178131873864</v>
       </c>
@@ -7786,7 +7799,7 @@
       <c r="B41" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="C41" s="11">
+      <c r="C41" s="44">
         <f>5*C16-10*C19+10*C22-5*C25+C28</f>
         <v>0.163459574200511</v>
       </c>
@@ -7878,18 +7891,18 @@
       <c r="A46" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="B46" s="11">
+      <c r="B46" s="44">
         <f>D32</f>
         <v>0.0107252298263534</v>
       </c>
       <c r="C46" s="4">
         <v>35</v>
       </c>
-      <c r="D46" s="11">
+      <c r="D46" s="44">
         <f>B46*C46</f>
         <v>0.37538304392237</v>
       </c>
-      <c r="E46" s="11">
+      <c r="E46" s="44">
         <f>IF($D$51=0,0,D46/$D$51)</f>
         <v>0.417651838388396</v>
       </c>
@@ -7904,18 +7917,18 @@
       <c r="A47" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="B47" s="11">
+      <c r="B47" s="44">
         <f>C40</f>
         <v>0.00971178131873864</v>
       </c>
       <c r="C47" s="4">
         <v>20</v>
       </c>
-      <c r="D47" s="11">
+      <c r="D47" s="44">
         <f>B47*C47</f>
         <v>0.194235626374773</v>
       </c>
-      <c r="E47" s="11">
+      <c r="E47" s="44">
         <f>IF($D$51=0,0,D47/$D$51)</f>
         <v>0.216106901335485</v>
       </c>
@@ -7930,18 +7943,18 @@
       <c r="A48" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="B48" s="11">
+      <c r="B48" s="44">
         <f>C41</f>
         <v>0.163459574200511</v>
       </c>
       <c r="C48" s="4">
         <v>2</v>
       </c>
-      <c r="D48" s="11">
+      <c r="D48" s="44">
         <f>B48*C48</f>
         <v>0.326919148401021</v>
       </c>
-      <c r="E48" s="11">
+      <c r="E48" s="44">
         <f>IF($D$51=0,0,D48/$D$51)</f>
         <v>0.363730822541606</v>
       </c>
@@ -7956,18 +7969,18 @@
       <c r="A49" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="B49" s="11">
+      <c r="B49" s="44">
         <f>D35</f>
         <v>3.15786753814843e-7</v>
       </c>
       <c r="C49" s="4">
         <v>5000</v>
       </c>
-      <c r="D49" s="11">
+      <c r="D49" s="44">
         <f>B49*C49</f>
         <v>0.00157893376907422</v>
       </c>
-      <c r="E49" s="11">
+      <c r="E49" s="44">
         <f>IF($D$51=0,0,D49/$D$51)</f>
         <v>0.00175672450320836</v>
       </c>
@@ -7982,18 +7995,18 @@
       <c r="A50" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B50" s="11">
+      <c r="B50" s="44">
         <f>D36</f>
         <v>3.38716534929428e-9</v>
       </c>
       <c r="C50" s="4">
         <v>200000</v>
       </c>
-      <c r="D50" s="11">
+      <c r="D50" s="44">
         <f>B50*C50</f>
         <v>0.000677433069858857</v>
       </c>
-      <c r="E50" s="11">
+      <c r="E50" s="44">
         <f>IF($D$51=0,0,D50/$D$51)</f>
         <v>0.000753713231304494</v>
       </c>
@@ -8014,11 +8027,11 @@
       <c r="C51" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D51" s="15">
+      <c r="D51" s="45">
         <f>SUM(D46:D50)</f>
         <v>0.898794185537097</v>
       </c>
-      <c r="E51" s="15">
+      <c r="E51" s="45">
         <f>SUM(E46:E50)</f>
         <v>1</v>
       </c>
@@ -8039,7 +8052,7 @@
       <c r="C52" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="D52" s="17">
+      <c r="D52" s="47">
         <f>D51-B52</f>
         <v>-0.0012058144629028</v>
       </c>
@@ -8119,18 +8132,18 @@
       <c r="B56" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="C56" s="11">
+      <c r="C56" s="44">
         <f>D32</f>
         <v>0.0107252298263534</v>
       </c>
-      <c r="D56" s="11">
+      <c r="D56" s="44">
         <f>C56-C57</f>
         <v>0.0107249140395996</v>
       </c>
       <c r="E56" s="4">
         <v>35</v>
       </c>
-      <c r="F56" s="11">
+      <c r="F56" s="44">
         <f>D56*E56</f>
         <v>0.375371991385986</v>
       </c>
@@ -8145,18 +8158,18 @@
       <c r="B57" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C57" s="11">
+      <c r="C57" s="44">
         <f>D35</f>
         <v>3.15786753814843e-7</v>
       </c>
-      <c r="D57" s="11">
+      <c r="D57" s="44">
         <f>C57-C58</f>
         <v>3.12399588465549e-7</v>
       </c>
       <c r="E57" s="4">
         <v>5000</v>
       </c>
-      <c r="F57" s="11">
+      <c r="F57" s="44">
         <f>D57*E57</f>
         <v>0.00156199794232774</v>
       </c>
@@ -8171,18 +8184,18 @@
       <c r="B58" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C58" s="11">
+      <c r="C58" s="44">
         <f>D36</f>
         <v>3.38716534929428e-9</v>
       </c>
-      <c r="D58" s="11">
+      <c r="D58" s="44">
         <f>C58</f>
         <v>3.38716534929428e-9</v>
       </c>
       <c r="E58" s="4">
         <v>200000</v>
       </c>
-      <c r="F58" s="11">
+      <c r="F58" s="44">
         <f>D58*E58</f>
         <v>0.000677433069858857</v>
       </c>
@@ -8206,7 +8219,7 @@
       <c r="E59" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F59" s="15">
+      <c r="F59" s="45">
         <f>SUM(F56:F58)</f>
         <v>0.377611422398173</v>
       </c>
@@ -8218,7 +8231,7 @@
       <c r="A60" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="B60" s="11">
+      <c r="B60" s="44">
         <f>B46*C46+B49*C49+B50*C50</f>
         <v>0.377639410761303</v>
       </c>
@@ -8242,7 +8255,7 @@
       <c r="A61" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B61" s="11">
+      <c r="B61" s="44">
         <f>B60-F59</f>
         <v>2.79883631299493e-5</v>
       </c>
@@ -8317,19 +8330,19 @@
       <c r="A65" s="4">
         <v>25</v>
       </c>
-      <c r="B65" s="11">
+      <c r="B65" s="44">
         <f>IF(OR($A65-3&lt;0,$A65&gt;$B$3),0,COMBIN($B$3-3,$A65-3)/COMBIN($B$3,$A65))</f>
         <v>0.0195778004766769</v>
       </c>
-      <c r="C65" s="11">
+      <c r="C65" s="44">
         <f>IF(OR($A65-4&lt;0,$A65&gt;$B$3),0,COMBIN($B$3-4,$A65-4)/COMBIN($B$3,$A65))</f>
         <v>0.00495070816651599</v>
       </c>
-      <c r="D65" s="11">
+      <c r="D65" s="44">
         <f>IF(OR($A65-5&lt;0,$A65&gt;$B$3),0,COMBIN($B$3-5,$A65-5)/COMBIN($B$3,$A65))</f>
         <v>0.00120889385461437</v>
       </c>
-      <c r="E65" s="11">
+      <c r="E65" s="44">
         <f>IF(OR($A65-15&lt;0,$A65&gt;$B$3),0,COMBIN($B$3-15,$A65-15)/COMBIN($B$3,$A65))</f>
         <v>7.13770475904925e-11</v>
       </c>
@@ -8345,19 +8358,19 @@
       <c r="A66" s="4">
         <v>30</v>
       </c>
-      <c r="B66" s="11">
+      <c r="B66" s="44">
         <f>IF(OR($A66-3&lt;0,$A66&gt;$B$3),0,COMBIN($B$3-3,$A66-3)/COMBIN($B$3,$A66))</f>
         <v>0.0345590738849166</v>
       </c>
-      <c r="C66" s="11">
+      <c r="C66" s="44">
         <f>IF(OR($A66-4&lt;0,$A66&gt;$B$3),0,COMBIN($B$3-4,$A66-4)/COMBIN($B$3,$A66))</f>
         <v>0.0107252298263534</v>
       </c>
-      <c r="D66" s="11">
+      <c r="D66" s="44">
         <f>IF(OR($A66-5&lt;0,$A66&gt;$B$3),0,COMBIN($B$3-5,$A66-5)/COMBIN($B$3,$A66))</f>
         <v>0.00324251134285104</v>
       </c>
-      <c r="E66" s="11">
+      <c r="E66" s="44">
         <f>IF(OR($A66-15&lt;0,$A66&gt;$B$3),0,COMBIN($B$3-15,$A66-15)/COMBIN($B$3,$A66))</f>
         <v>3.38716534929428e-9</v>
       </c>
@@ -8373,19 +8386,19 @@
       <c r="A67" s="4">
         <v>35</v>
       </c>
-      <c r="B67" s="11">
+      <c r="B67" s="44">
         <f>IF(OR($A67-3&lt;0,$A67&gt;$B$3),0,COMBIN($B$3-3,$A67-3)/COMBIN($B$3,$A67))</f>
         <v>0.0557116104868914</v>
       </c>
-      <c r="C67" s="11">
+      <c r="C67" s="44">
         <f>IF(OR($A67-4&lt;0,$A67&gt;$B$3),0,COMBIN($B$3-4,$A67-4)/COMBIN($B$3,$A67))</f>
         <v>0.0204916268457532</v>
       </c>
-      <c r="D67" s="11">
+      <c r="D67" s="44">
         <f>IF(OR($A67-5&lt;0,$A67&gt;$B$3),0,COMBIN($B$3-5,$A67-5)/COMBIN($B$3,$A67))</f>
         <v>0.00738651665370171</v>
       </c>
-      <c r="E67" s="11">
+      <c r="E67" s="44">
         <f>IF(OR($A67-15&lt;0,$A67&gt;$B$3),0,COMBIN($B$3-15,$A67-15)/COMBIN($B$3,$A67))</f>
         <v>7.09224884979426e-8</v>
       </c>
@@ -8401,19 +8414,19 @@
       <c r="A68" s="4">
         <v>40</v>
       </c>
-      <c r="B68" s="11">
+      <c r="B68" s="44">
         <f>IF(OR($A68-3&lt;0,$A68&gt;$B$3),0,COMBIN($B$3-3,$A68-3)/COMBIN($B$3,$A68))</f>
         <v>0.0840994211780729</v>
       </c>
-      <c r="C68" s="11">
+      <c r="C68" s="44">
         <f>IF(OR($A68-4&lt;0,$A68&gt;$B$3),0,COMBIN($B$3-4,$A68-4)/COMBIN($B$3,$A68))</f>
         <v>0.0357664205010195</v>
       </c>
-      <c r="D68" s="11">
+      <c r="D68" s="44">
         <f>IF(OR($A68-5&lt;0,$A68&gt;$B$3),0,COMBIN($B$3-5,$A68-5)/COMBIN($B$3,$A68))</f>
         <v>0.0149719899771709</v>
       </c>
-      <c r="E68" s="11">
+      <c r="E68" s="44">
         <f>IF(OR($A68-15&lt;0,$A68&gt;$B$3),0,COMBIN($B$3-15,$A68-15)/COMBIN($B$3,$A68))</f>
         <v>8.7836560910134e-7</v>
       </c>
@@ -8429,19 +8442,19 @@
       <c r="A69" s="4">
         <v>45</v>
       </c>
-      <c r="B69" s="11">
+      <c r="B69" s="44">
         <f>IF(OR($A69-3&lt;0,$A69&gt;$B$3),0,COMBIN($B$3-3,$A69-3)/COMBIN($B$3,$A69))</f>
         <v>0.120786516853933</v>
       </c>
-      <c r="C69" s="11">
+      <c r="C69" s="44">
         <f>IF(OR($A69-4&lt;0,$A69&gt;$B$3),0,COMBIN($B$3-4,$A69-4)/COMBIN($B$3,$A69))</f>
         <v>0.0583107322743123</v>
       </c>
-      <c r="D69" s="11">
+      <c r="D69" s="44">
         <f>IF(OR($A69-5&lt;0,$A69&gt;$B$3),0,COMBIN($B$3-5,$A69-5)/COMBIN($B$3,$A69))</f>
         <v>0.027799302595893</v>
       </c>
-      <c r="E69" s="11">
+      <c r="E69" s="44">
         <f>IF(OR($A69-15&lt;0,$A69&gt;$B$3),0,COMBIN($B$3-15,$A69-15)/COMBIN($B$3,$A69))</f>
         <v>7.5305677530072e-6</v>
       </c>
@@ -8516,7 +8529,7 @@
       <c r="A73" s="4">
         <v>1</v>
       </c>
-      <c r="B73" s="11">
+      <c r="B73" s="44">
         <f>$D32</f>
         <v>0.0107252298263534</v>
       </c>
@@ -8524,11 +8537,11 @@
         <f>A73*B73</f>
         <v>0.0107252298263534</v>
       </c>
-      <c r="D73" s="11">
+      <c r="D73" s="44">
         <f>1-(1-B73)^A73</f>
         <v>0.0107252298263534</v>
       </c>
-      <c r="E73" s="11">
+      <c r="E73" s="44">
         <f>$F59</f>
         <v>0.377611422398173</v>
       </c>
@@ -8543,7 +8556,7 @@
       <c r="A74" s="4">
         <v>2</v>
       </c>
-      <c r="B74" s="11">
+      <c r="B74" s="44">
         <f>$D32</f>
         <v>0.0107252298263534</v>
       </c>
@@ -8551,11 +8564,11 @@
         <f>A74*B74</f>
         <v>0.0214504596527068</v>
       </c>
-      <c r="D74" s="11">
+      <c r="D74" s="44">
         <f>1-(1-B74)^A74</f>
         <v>0.0213354290978787</v>
       </c>
-      <c r="E74" s="11">
+      <c r="E74" s="44">
         <f>$F59</f>
         <v>0.377611422398173</v>
       </c>
@@ -8570,7 +8583,7 @@
       <c r="A75" s="4">
         <v>3</v>
       </c>
-      <c r="B75" s="11">
+      <c r="B75" s="44">
         <f>$D32</f>
         <v>0.0107252298263534</v>
       </c>
@@ -8578,11 +8591,11 @@
         <f>A75*B75</f>
         <v>0.0321756894790603</v>
       </c>
-      <c r="D75" s="11">
+      <c r="D75" s="44">
         <f>1-(1-B75)^A75</f>
         <v>0.0318318315437134</v>
       </c>
-      <c r="E75" s="11">
+      <c r="E75" s="44">
         <f>$F59</f>
         <v>0.377611422398173</v>
       </c>
@@ -8597,7 +8610,7 @@
       <c r="A76" s="4">
         <v>4</v>
       </c>
-      <c r="B76" s="11">
+      <c r="B76" s="44">
         <f>$D32</f>
         <v>0.0107252298263534</v>
       </c>
@@ -8605,11 +8618,11 @@
         <f>A76*B76</f>
         <v>0.0429009193054137</v>
       </c>
-      <c r="D76" s="11">
+      <c r="D76" s="44">
         <f>1-(1-B76)^A76</f>
         <v>0.0422156576609667</v>
       </c>
-      <c r="E76" s="11">
+      <c r="E76" s="44">
         <f>$F59</f>
         <v>0.377611422398173</v>
       </c>
@@ -8624,7 +8637,7 @@
       <c r="A77" s="4">
         <v>5</v>
       </c>
-      <c r="B77" s="11">
+      <c r="B77" s="44">
         <f>$D32</f>
         <v>0.0107252298263534</v>
       </c>
@@ -8632,11 +8645,11 @@
         <f>A77*B77</f>
         <v>0.0536261491317671</v>
       </c>
-      <c r="D77" s="11">
+      <c r="D77" s="44">
         <f>1-(1-B77)^A77</f>
         <v>0.0524881148566355</v>
       </c>
-      <c r="E77" s="11">
+      <c r="E77" s="44">
         <f>$F59</f>
         <v>0.377611422398173</v>
       </c>
@@ -8795,7 +8808,7 @@
       <c r="B85" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C85" s="11">
+      <c r="C85" s="44">
         <f>IF(OR($B$84-$B$83&lt;0,$B$84&gt;$B$82),0,COMBIN($B$82-$B$83,$B$84-$B$83)/COMBIN($B$82,$B$84))</f>
         <v>0.00139853398623526</v>
       </c>
@@ -8815,7 +8828,7 @@
       <c r="B86" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C86" s="11">
+      <c r="C86" s="44">
         <f>IF(OR($B$84-5&lt;0,$B$84&gt;$B$82),0,COMBIN($B$82-5,$B$84-5)/COMBIN($B$82,$B$84))</f>
         <v>0.316437139435403</v>
       </c>
@@ -8835,7 +8848,7 @@
       <c r="B87" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C87" s="11">
+      <c r="C87" s="44">
         <f>IF(OR($B$84-4&lt;0,$B$84&gt;$B$82),0,COMBIN($B$82-4,$B$84-4)/COMBIN($B$82,$B$84))</f>
         <v>0.401197087498457</v>
       </c>
@@ -8973,7 +8986,7 @@
       <c r="B94" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C94" s="11">
+      <c r="C94" s="44">
         <f>IF(OR($B$93-5&lt;0,$B$93&gt;$B$92),0,COMBIN($B$92-5,$B$93-5)/COMBIN($B$92,$B$93))</f>
         <v>0.0565217391304348</v>
       </c>
@@ -9036,7 +9049,7 @@
       <c r="A97" s="4">
         <v>10</v>
       </c>
-      <c r="B97" s="11">
+      <c r="B97" s="44">
         <f>IF(OR($A97-5&lt;0,$A97&gt;$B$92),0,COMBIN($B$92-5,$A97-5)/COMBIN($B$92,$A97))</f>
         <v>0.00474308300395257</v>
       </c>
@@ -9061,7 +9074,7 @@
       <c r="A98" s="4">
         <v>15</v>
       </c>
-      <c r="B98" s="11">
+      <c r="B98" s="44">
         <f>IF(OR($A98-5&lt;0,$A98&gt;$B$92),0,COMBIN($B$92-5,$A98-5)/COMBIN($B$92,$A98))</f>
         <v>0.0565217391304348</v>
       </c>
@@ -9086,7 +9099,7 @@
       <c r="A99" s="4">
         <v>18</v>
       </c>
-      <c r="B99" s="11">
+      <c r="B99" s="44">
         <f>IF(OR($A99-5&lt;0,$A99&gt;$B$92),0,COMBIN($B$92-5,$A99-5)/COMBIN($B$92,$A99))</f>
         <v>0.161264822134387</v>
       </c>
@@ -9111,7 +9124,7 @@
       <c r="A100" s="4">
         <v>20</v>
       </c>
-      <c r="B100" s="11">
+      <c r="B100" s="44">
         <f>IF(OR($A100-5&lt;0,$A100&gt;$B$92),0,COMBIN($B$92-5,$A100-5)/COMBIN($B$92,$A100))</f>
         <v>0.291812535290796</v>
       </c>
@@ -9136,7 +9149,7 @@
       <c r="A101" s="4">
         <v>25</v>
       </c>
-      <c r="B101" s="11">
+      <c r="B101" s="44">
         <f>IF(OR($A101-5&lt;0,$A101&gt;$B$92),0,COMBIN($B$92-5,$A101-5)/COMBIN($B$92,$A101))</f>
         <v>1</v>
       </c>
@@ -9303,7 +9316,7 @@
       <c r="B109" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C109" s="11">
+      <c r="C109" s="44">
         <f>IF(OR($B$108-5&lt;0,$B$108&gt;$B$107),0,COMBIN($B$107-5,$B$108-5)/COMBIN($B$107,$B$108))</f>
         <v>0.00324251134285104</v>
       </c>
@@ -9323,7 +9336,7 @@
       <c r="B110" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C110" s="11">
+      <c r="C110" s="44">
         <f>C40</f>
         <v>0.00971178131873864</v>
       </c>
